--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.29499683332392</v>
+        <v>73.99753534943626</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.86894529948697</v>
+        <v>80.35325948539298</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61.95578374561016</v>
+        <v>59.16751236553726</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.763424339571324</v>
+        <v>1.750729472014877</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.094654287023305e-24</v>
+        <v>2725019.139206441</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2273.43</v>
+        <v>2099.45537019839</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1402</v>
+        <v>1400.084868522487</v>
       </c>
     </row>
     <row r="4">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>4195.963333333333</v>
+        <v>4020.073572054211</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>83.86894529948697</v>
+        <v>80.35325948539298</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>83.86894529948697</v>
+        <v>80.35325948539298</v>
       </c>
     </row>
     <row r="15">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>74.29782130721566</v>
+        <v>70.77158231640915</v>
       </c>
       <c r="F11" t="n">
-        <v>58.74885091248429</v>
+        <v>55.96057953241138</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>61.95578374561016</v>
+        <v>59.16751236553726</v>
       </c>
     </row>
     <row r="13">
@@ -1054,11 +1054,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63.20934720448355</v>
+        <v>60.57137801737341</v>
       </c>
       <c r="C2" t="n">
-        <v>70.25217201890374</v>
+        <v>67.28445668340483</v>
       </c>
       <c r="D2" t="n">
-        <v>77.29499683332392</v>
+        <v>73.99753534943626</v>
       </c>
       <c r="E2" t="n">
-        <v>84.33782164774412</v>
+        <v>80.71061401546768</v>
       </c>
       <c r="F2" t="n">
-        <v>91.38064646216431</v>
+        <v>87.42369268149911</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63.20934720448355</v>
+        <v>60.57137801737341</v>
       </c>
       <c r="C3" t="n">
-        <v>70.25217201890374</v>
+        <v>67.28445668340483</v>
       </c>
       <c r="D3" t="n">
-        <v>77.29499683332392</v>
+        <v>73.99753534943626</v>
       </c>
       <c r="E3" t="n">
-        <v>84.33782164774412</v>
+        <v>80.71061401546768</v>
       </c>
       <c r="F3" t="n">
-        <v>91.38064646216431</v>
+        <v>87.42369268149911</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63.20934720448355</v>
+        <v>60.57137801737341</v>
       </c>
       <c r="C4" t="n">
-        <v>70.25217201890374</v>
+        <v>67.28445668340483</v>
       </c>
       <c r="D4" t="n">
-        <v>77.29499683332392</v>
+        <v>73.99753534943626</v>
       </c>
       <c r="E4" t="n">
-        <v>84.33782164774412</v>
+        <v>80.71061401546768</v>
       </c>
       <c r="F4" t="n">
-        <v>91.38064646216431</v>
+        <v>87.42369268149911</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.20934720448355</v>
+        <v>60.57137801737341</v>
       </c>
       <c r="C5" t="n">
-        <v>70.25217201890374</v>
+        <v>67.28445668340483</v>
       </c>
       <c r="D5" t="n">
-        <v>77.29499683332392</v>
+        <v>73.99753534943626</v>
       </c>
       <c r="E5" t="n">
-        <v>84.33782164774412</v>
+        <v>80.71061401546768</v>
       </c>
       <c r="F5" t="n">
-        <v>91.38064646216431</v>
+        <v>87.42369268149911</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.20934720448355</v>
+        <v>60.57137801737341</v>
       </c>
       <c r="C6" t="n">
-        <v>70.25217201890374</v>
+        <v>67.28445668340483</v>
       </c>
       <c r="D6" t="n">
-        <v>77.29499683332392</v>
+        <v>73.99753534943626</v>
       </c>
       <c r="E6" t="n">
-        <v>84.33782164774412</v>
+        <v>80.71061401546768</v>
       </c>
       <c r="F6" t="n">
-        <v>91.38064646216431</v>
+        <v>87.42369268149911</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>83.94</v>
+        <v>80.64</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>85.19</v>
+        <v>81.89</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>85.59999999999999</v>
+        <v>82.31</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2725019.139206441</v>
+        <v>2725019.139206442</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2725019.139206442</v>
+        <v>2725019.139206441</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75.59999999999999</v>
+        <v>76.45999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2725019.139206441</v>
+        <v>2725019.139206442</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.45999999999999</v>
+        <v>77.94</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77.94</v>
+        <v>76.17</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.17</v>
+        <v>80.58</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2725019.139206442</v>
+        <v>2725019.139206441</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.99753534943626</v>
+        <v>78.93194388024949</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.16751236553726</v>
+        <v>75.61554080158139</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2725019.139206442</v>
+        <v>62640.3845695215</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50</v>
+        <v>1.149356781908019</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>70.77158231640915</v>
+        <v>91.57288580773445</v>
       </c>
       <c r="F11" t="n">
-        <v>55.96057953241138</v>
+        <v>72.40860796845551</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>59.16751236553726</v>
+        <v>75.61554080158139</v>
       </c>
     </row>
     <row r="13">
@@ -1054,11 +1054,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60.57137801737341</v>
+        <v>62.50135249055397</v>
       </c>
       <c r="C2" t="n">
-        <v>67.28445668340483</v>
+        <v>69.06149456730344</v>
       </c>
       <c r="D2" t="n">
-        <v>73.99753534943626</v>
+        <v>75.62163664405293</v>
       </c>
       <c r="E2" t="n">
-        <v>80.71061401546768</v>
+        <v>82.18177872080241</v>
       </c>
       <c r="F2" t="n">
-        <v>87.42369268149911</v>
+        <v>88.74192079755188</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.57137801737341</v>
+        <v>64.15650610865225</v>
       </c>
       <c r="C3" t="n">
-        <v>67.28445668340483</v>
+        <v>70.71664818540174</v>
       </c>
       <c r="D3" t="n">
-        <v>73.99753534943626</v>
+        <v>77.27679026215121</v>
       </c>
       <c r="E3" t="n">
-        <v>80.71061401546768</v>
+        <v>83.8369323389007</v>
       </c>
       <c r="F3" t="n">
-        <v>87.42369268149911</v>
+        <v>90.39707441565017</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60.57137801737341</v>
+        <v>65.81165972675053</v>
       </c>
       <c r="C4" t="n">
-        <v>67.28445668340483</v>
+        <v>72.37180180350002</v>
       </c>
       <c r="D4" t="n">
-        <v>73.99753534943626</v>
+        <v>78.93194388024949</v>
       </c>
       <c r="E4" t="n">
-        <v>80.71061401546768</v>
+        <v>85.49208595699898</v>
       </c>
       <c r="F4" t="n">
-        <v>87.42369268149911</v>
+        <v>92.05222803374845</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.57137801737341</v>
+        <v>67.46681334484882</v>
       </c>
       <c r="C5" t="n">
-        <v>67.28445668340483</v>
+        <v>74.0269554215983</v>
       </c>
       <c r="D5" t="n">
-        <v>73.99753534943626</v>
+        <v>80.58709749834779</v>
       </c>
       <c r="E5" t="n">
-        <v>80.71061401546768</v>
+        <v>87.14723957509727</v>
       </c>
       <c r="F5" t="n">
-        <v>87.42369268149911</v>
+        <v>93.70738165184673</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60.57137801737341</v>
+        <v>69.12196696294711</v>
       </c>
       <c r="C6" t="n">
-        <v>67.28445668340483</v>
+        <v>75.68210903969658</v>
       </c>
       <c r="D6" t="n">
-        <v>73.99753534943626</v>
+        <v>82.24225111644607</v>
       </c>
       <c r="E6" t="n">
-        <v>80.71061401546768</v>
+        <v>88.80239319319556</v>
       </c>
       <c r="F6" t="n">
-        <v>87.42369268149911</v>
+        <v>95.36253526994503</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>80.64</v>
+        <v>79.72</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>81.89</v>
+        <v>79.87</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>82.31</v>
+        <v>79.92</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80.58</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>62640.3845695215</v>
+        <v>23127.1583494094</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.149356781908019</v>
+        <v>0.4243485489086201</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72.58</v>
+        <v>70.09</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23127.1583494094</v>
+        <v>10828.66668839953</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4243485489086201</v>
+        <v>0.1986897363875575</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -1268,7 +1268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1284,13 +1284,6 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
           <t>LR2 FFA forward curve is CONSTRUCTED (no market anchor) — built from the 12M TC + spot, not a Baltic / $MT / Worldscale series. Treat its dividend-strip contribution as indicative.</t>
         </is>
       </c>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70.09</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10828.66668839953</v>
+        <v>38043.40124750169</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1986897363875575</v>
+        <v>0.6980391568658926</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.93194388024949</v>
+        <v>76.12769620826306</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80.35325948539298</v>
+        <v>77.4657057214697</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75.61554080158139</v>
+        <v>73.00567401078092</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.750729472014877</v>
+        <v>1.770971367861763</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38043.40124750169</v>
+        <v>53301.49046672191</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6980391568658926</v>
+        <v>0.9500624718915445</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1400.084868522487</v>
+        <v>1210.693233020247</v>
       </c>
     </row>
     <row r="4">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>984.3</v>
+        <v>984.321</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>602.8</v>
+        <v>163.273</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-789.1</v>
+        <v>-589.056</v>
       </c>
     </row>
     <row r="8">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>69.069</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>4020.073572054211</v>
+        <v>3875.288936551971</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50030000</v>
+        <v>50025865</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80.35325948539298</v>
+        <v>77.4657057214697</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80.35325948539298</v>
+        <v>77.4657057214697</v>
       </c>
     </row>
     <row r="15">
@@ -833,7 +833,7 @@
         <v>69375</v>
       </c>
       <c r="D2" t="n">
-        <v>3.957938336997801</v>
+        <v>3.811939683601673</v>
       </c>
       <c r="E2" t="n">
         <v>0.45</v>
@@ -855,7 +855,7 @@
         <v>80750</v>
       </c>
       <c r="D3" t="n">
-        <v>5.395030081950829</v>
+        <v>5.163346600803404</v>
       </c>
       <c r="E3" t="n">
         <v>0.45</v>
@@ -877,7 +877,7 @@
         <v>75500</v>
       </c>
       <c r="D4" t="n">
-        <v>4.898125224865081</v>
+        <v>4.687851574380573</v>
       </c>
       <c r="E4" t="n">
         <v>0.45</v>
@@ -899,7 +899,7 @@
         <v>59750</v>
       </c>
       <c r="D5" t="n">
-        <v>3.112485108934639</v>
+        <v>2.998592927878409</v>
       </c>
       <c r="E5" t="n">
         <v>0.45</v>
@@ -921,7 +921,7 @@
         <v>55375</v>
       </c>
       <c r="D6" t="n">
-        <v>2.763936737957226</v>
+        <v>2.660741198577976</v>
       </c>
       <c r="E6" t="n">
         <v>0.45</v>
@@ -943,7 +943,7 @@
         <v>65000</v>
       </c>
       <c r="D7" t="n">
-        <v>3.806006995802519</v>
+        <v>3.64927033245702</v>
       </c>
       <c r="E7" t="n">
         <v>0.45</v>
@@ -965,7 +965,7 @@
         <v>68500</v>
       </c>
       <c r="D8" t="n">
-        <v>4.301124425344793</v>
+        <v>4.112252331868724</v>
       </c>
       <c r="E8" t="n">
         <v>0.45</v>
@@ -987,7 +987,7 @@
         <v>52750</v>
       </c>
       <c r="D9" t="n">
-        <v>2.613792824305417</v>
+        <v>2.51058487444445</v>
       </c>
       <c r="E9" t="n">
         <v>0.45</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>91.57288580773445</v>
+        <v>88.27226948168264</v>
       </c>
       <c r="F11" t="n">
-        <v>72.40860796845551</v>
+        <v>69.79874117765505</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>75.61554080158139</v>
+        <v>73.00567401078092</v>
       </c>
     </row>
     <row r="13">
@@ -1054,7 +1054,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62.50135249055397</v>
+        <v>60.50587301364492</v>
       </c>
       <c r="C2" t="n">
-        <v>69.06149456730344</v>
+        <v>66.73171554090408</v>
       </c>
       <c r="D2" t="n">
-        <v>75.62163664405293</v>
+        <v>72.95755806816322</v>
       </c>
       <c r="E2" t="n">
-        <v>82.18177872080241</v>
+        <v>79.18340059542237</v>
       </c>
       <c r="F2" t="n">
-        <v>88.74192079755188</v>
+        <v>85.4092431226815</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64.15650610865225</v>
+        <v>62.09094208369484</v>
       </c>
       <c r="C3" t="n">
-        <v>70.71664818540174</v>
+        <v>68.31678461095399</v>
       </c>
       <c r="D3" t="n">
-        <v>77.27679026215121</v>
+        <v>74.54262713821313</v>
       </c>
       <c r="E3" t="n">
-        <v>83.8369323389007</v>
+        <v>80.76846966547228</v>
       </c>
       <c r="F3" t="n">
-        <v>90.39707441565017</v>
+        <v>86.99431219273143</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65.81165972675053</v>
+        <v>63.67601115374477</v>
       </c>
       <c r="C4" t="n">
-        <v>72.37180180350002</v>
+        <v>69.90185368100393</v>
       </c>
       <c r="D4" t="n">
-        <v>78.93194388024949</v>
+        <v>76.12769620826306</v>
       </c>
       <c r="E4" t="n">
-        <v>85.49208595699898</v>
+        <v>82.35353873552222</v>
       </c>
       <c r="F4" t="n">
-        <v>92.05222803374845</v>
+        <v>88.57938126278135</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.46681334484882</v>
+        <v>65.26108022379469</v>
       </c>
       <c r="C5" t="n">
-        <v>74.0269554215983</v>
+        <v>71.48692275105384</v>
       </c>
       <c r="D5" t="n">
-        <v>80.58709749834779</v>
+        <v>77.71276527831299</v>
       </c>
       <c r="E5" t="n">
-        <v>87.14723957509727</v>
+        <v>83.93860780557213</v>
       </c>
       <c r="F5" t="n">
-        <v>93.70738165184673</v>
+        <v>90.16445033283128</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69.12196696294711</v>
+        <v>66.84614929384462</v>
       </c>
       <c r="C6" t="n">
-        <v>75.68210903969658</v>
+        <v>73.07199182110377</v>
       </c>
       <c r="D6" t="n">
-        <v>82.24225111644607</v>
+        <v>79.29783434836291</v>
       </c>
       <c r="E6" t="n">
-        <v>88.80239319319556</v>
+        <v>85.52367687562206</v>
       </c>
       <c r="F6" t="n">
-        <v>95.36253526994503</v>
+        <v>91.74951940288121</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>79.72</v>
+        <v>76.89</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>79.87</v>
+        <v>77.03</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>79.92</v>
+        <v>77.08</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75.59999999999999</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53301.49046672191</v>
+        <v>21074.55952441736</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9500624718915445</v>
+        <v>0.3756395541752068</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69.53</v>
+        <v>73.01000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21074.55952441736</v>
+        <v>39550.62536942893</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3756395541752068</v>
+        <v>0.7049627425858924</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73.01000000000001</v>
+        <v>76.25</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39550.62536942893</v>
+        <v>56752.47977685342</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7049627425858924</v>
+        <v>1.011573986968254</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.25</v>
+        <v>79.31999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56752.47977685342</v>
+        <v>73051.76774932041</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.011573986968254</v>
+        <v>1.302097604330552</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79.31999999999999</v>
+        <v>77.28</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>73051.76774932041</v>
+        <v>62220.97052983095</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.302097604330552</v>
+        <v>1.109046080089807</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77.28</v>
+        <v>77.87</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>62220.97052983095</v>
+        <v>65353.40698056568</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.109046080089807</v>
+        <v>1.164879609159434</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>65353.40698056568</v>
+        <v>65353.40698056567</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>65353.40698056567</v>
+        <v>65353.40698056568</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77.87</v>
+        <v>76.48999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>65353.40698056568</v>
+        <v>58026.69121444038</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.164879609159434</v>
+        <v>1.034285930996576</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.12769620826306</v>
+        <v>75.85748392835102</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77.4657057214697</v>
+        <v>77.13284058229945</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>73.00567401078092</v>
+        <v>72.88165173580465</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.770971367861763</v>
+        <v>1.76948884549691</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58026.69121444038</v>
+        <v>59336.89310930172</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.034285930996576</v>
+        <v>1.05985695673461</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2099.45537019839</v>
+        <v>2081.687672336287</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1210.693233020247</v>
+        <v>1211.809064367013</v>
       </c>
     </row>
     <row r="4">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3875.288936551971</v>
+        <v>3858.637070036633</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.4657057214697</v>
+        <v>77.13284058229945</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>77.4657057214697</v>
+        <v>77.13284058229945</v>
       </c>
     </row>
     <row r="15">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>88.27226948168264</v>
+        <v>88.11542241691149</v>
       </c>
       <c r="F11" t="n">
-        <v>69.79874117765505</v>
+        <v>69.67471890267878</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>73.00567401078092</v>
+        <v>72.88165173580465</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60.50587301364492</v>
+        <v>60.28970318971528</v>
       </c>
       <c r="C2" t="n">
-        <v>66.73171554090408</v>
+        <v>66.48852448898322</v>
       </c>
       <c r="D2" t="n">
-        <v>72.95755806816322</v>
+        <v>72.68734578825116</v>
       </c>
       <c r="E2" t="n">
-        <v>79.18340059542237</v>
+        <v>78.88616708751911</v>
       </c>
       <c r="F2" t="n">
-        <v>85.4092431226815</v>
+        <v>85.08498838678705</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62.09094208369484</v>
+        <v>61.8747722597652</v>
       </c>
       <c r="C3" t="n">
-        <v>68.31678461095399</v>
+        <v>68.07359355903314</v>
       </c>
       <c r="D3" t="n">
-        <v>74.54262713821313</v>
+        <v>74.27241485830109</v>
       </c>
       <c r="E3" t="n">
-        <v>80.76846966547228</v>
+        <v>80.47123615756904</v>
       </c>
       <c r="F3" t="n">
-        <v>86.99431219273143</v>
+        <v>86.67005745683697</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63.67601115374477</v>
+        <v>63.45984132981513</v>
       </c>
       <c r="C4" t="n">
-        <v>69.90185368100393</v>
+        <v>69.65866262908307</v>
       </c>
       <c r="D4" t="n">
-        <v>76.12769620826306</v>
+        <v>75.85748392835102</v>
       </c>
       <c r="E4" t="n">
-        <v>82.35353873552222</v>
+        <v>82.05630522761896</v>
       </c>
       <c r="F4" t="n">
-        <v>88.57938126278135</v>
+        <v>88.2551265268869</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.26108022379469</v>
+        <v>65.04491039986505</v>
       </c>
       <c r="C5" t="n">
-        <v>71.48692275105384</v>
+        <v>71.24373169913298</v>
       </c>
       <c r="D5" t="n">
-        <v>77.71276527831299</v>
+        <v>77.44255299840093</v>
       </c>
       <c r="E5" t="n">
-        <v>83.93860780557213</v>
+        <v>83.64137429766888</v>
       </c>
       <c r="F5" t="n">
-        <v>90.16445033283128</v>
+        <v>89.84019559693681</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.84614929384462</v>
+        <v>66.62997946991497</v>
       </c>
       <c r="C6" t="n">
-        <v>73.07199182110377</v>
+        <v>72.82880076918291</v>
       </c>
       <c r="D6" t="n">
-        <v>79.29783434836291</v>
+        <v>79.02762206845085</v>
       </c>
       <c r="E6" t="n">
-        <v>85.52367687562206</v>
+        <v>85.22644336771882</v>
       </c>
       <c r="F6" t="n">
-        <v>91.74951940288121</v>
+        <v>91.42526466698673</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>76.89</v>
+        <v>76.62</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>77.03</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>77.08</v>
+        <v>76.81</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.48999999999999</v>
+        <v>77.98</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59336.89310930172</v>
+        <v>67231.07054978496</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.05985695673461</v>
+        <v>1.20086027591045</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67231.07054978496</v>
+        <v>67231.07054978497</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77.98</v>
+        <v>79.48999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67231.07054978497</v>
+        <v>75231.21010356319</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.20086027591045</v>
+        <v>1.343756257088649</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79.48999999999999</v>
+        <v>77.36499999999999</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75231.21010356319</v>
+        <v>63972.73556596135</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.343756257088649</v>
+        <v>1.142660919337872</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77.36499999999999</v>
+        <v>76.08</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63972.73556596135</v>
+        <v>57164.66978675268</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.142660919337872</v>
+        <v>1.021057385686225</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.85748392835102</v>
+        <v>73.33575039357001</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77.13284058229945</v>
+        <v>76.42261809795509</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>72.88165173580465</v>
+        <v>66.13305908333815</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.76948884549691</v>
+        <v>1.715697285094236</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57164.66978675268</v>
+        <v>71456.09659505378</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.021057385686225</v>
+        <v>1.3814208420171</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2081.687672336287</v>
+        <v>1576.69607308248</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1211.809064367013</v>
+        <v>1246.96996464278</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>205.3333333333333</v>
+        <v>244.8</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>984.321</v>
+        <v>1838.782</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>163.273</v>
+        <v>153.195</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-589.056</v>
+        <v>-855</v>
       </c>
     </row>
     <row r="8">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-572.8</v>
+        <v>-644.321</v>
       </c>
     </row>
     <row r="10">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69.069</v>
+        <v>90.208</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3858.637070036633</v>
+        <v>3827.34803772526</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50025865</v>
+        <v>50081352</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.13284058229945</v>
+        <v>76.42261809795509</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>77.13284058229945</v>
+        <v>76.42261809795509</v>
       </c>
     </row>
     <row r="15">
@@ -830,10 +830,10 @@
         <v>75000</v>
       </c>
       <c r="C2" t="n">
-        <v>69375</v>
+        <v>57773.96</v>
       </c>
       <c r="D2" t="n">
-        <v>3.811939683601673</v>
+        <v>2.536597741136262</v>
       </c>
       <c r="E2" t="n">
         <v>0.45</v>
@@ -852,10 +852,10 @@
         <v>88000</v>
       </c>
       <c r="C3" t="n">
-        <v>80750</v>
+        <v>65573.96000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>5.163346600803404</v>
+        <v>3.542044726672914</v>
       </c>
       <c r="E3" t="n">
         <v>0.45</v>
@@ -874,10 +874,10 @@
         <v>82000</v>
       </c>
       <c r="C4" t="n">
-        <v>75500</v>
+        <v>61973.96</v>
       </c>
       <c r="D4" t="n">
-        <v>4.687851574380573</v>
+        <v>3.217027196195702</v>
       </c>
       <c r="E4" t="n">
         <v>0.45</v>
@@ -896,10 +896,10 @@
         <v>64000</v>
       </c>
       <c r="C5" t="n">
-        <v>59750</v>
+        <v>51173.96</v>
       </c>
       <c r="D5" t="n">
-        <v>2.998592927878409</v>
+        <v>1.99550360244368</v>
       </c>
       <c r="E5" t="n">
         <v>0.45</v>
@@ -918,10 +918,10 @@
         <v>59000</v>
       </c>
       <c r="C6" t="n">
-        <v>55375</v>
+        <v>48173.96</v>
       </c>
       <c r="D6" t="n">
-        <v>2.660741198577976</v>
+        <v>1.779426994228311</v>
       </c>
       <c r="E6" t="n">
         <v>0.45</v>
@@ -940,10 +940,10 @@
         <v>70000</v>
       </c>
       <c r="C7" t="n">
-        <v>65000</v>
+        <v>54773.96</v>
       </c>
       <c r="D7" t="n">
-        <v>3.64927033245702</v>
+        <v>2.484835134467815</v>
       </c>
       <c r="E7" t="n">
         <v>0.45</v>
@@ -962,10 +962,10 @@
         <v>74000</v>
       </c>
       <c r="C8" t="n">
-        <v>68500</v>
+        <v>57173.96</v>
       </c>
       <c r="D8" t="n">
-        <v>4.112252331868724</v>
+        <v>2.838441822741726</v>
       </c>
       <c r="E8" t="n">
         <v>0.45</v>
@@ -984,10 +984,10 @@
         <v>56000</v>
       </c>
       <c r="C9" t="n">
-        <v>52750</v>
+        <v>46373.96</v>
       </c>
       <c r="D9" t="n">
-        <v>2.51058487444445</v>
+        <v>1.699075229763166</v>
       </c>
       <c r="E9" t="n">
         <v>0.45</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>88.11542241691149</v>
+        <v>79.58068985311942</v>
       </c>
       <c r="F11" t="n">
-        <v>69.67471890267878</v>
+        <v>62.92612625021227</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>72.88165173580465</v>
+        <v>66.13305908333815</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60.28970318971528</v>
+        <v>60.32537849359611</v>
       </c>
       <c r="C2" t="n">
-        <v>66.48852448898322</v>
+        <v>65.75134329041376</v>
       </c>
       <c r="D2" t="n">
-        <v>72.68734578825116</v>
+        <v>71.17730808723141</v>
       </c>
       <c r="E2" t="n">
-        <v>78.88616708751911</v>
+        <v>76.60327288404908</v>
       </c>
       <c r="F2" t="n">
-        <v>85.08498838678705</v>
+        <v>82.02923768086673</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.8747722597652</v>
+        <v>61.4045996467654</v>
       </c>
       <c r="C3" t="n">
-        <v>68.07359355903314</v>
+        <v>66.83056444358306</v>
       </c>
       <c r="D3" t="n">
-        <v>74.27241485830109</v>
+        <v>72.25652924040071</v>
       </c>
       <c r="E3" t="n">
-        <v>80.47123615756904</v>
+        <v>77.68249403721838</v>
       </c>
       <c r="F3" t="n">
-        <v>86.67005745683697</v>
+        <v>83.10845883403601</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63.45984132981513</v>
+        <v>62.4838207999347</v>
       </c>
       <c r="C4" t="n">
-        <v>69.65866262908307</v>
+        <v>67.90978559675236</v>
       </c>
       <c r="D4" t="n">
-        <v>75.85748392835102</v>
+        <v>73.33575039357001</v>
       </c>
       <c r="E4" t="n">
-        <v>82.05630522761896</v>
+        <v>78.76171519038766</v>
       </c>
       <c r="F4" t="n">
-        <v>88.2551265268869</v>
+        <v>84.18767998720531</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.04491039986505</v>
+        <v>63.56304195310399</v>
       </c>
       <c r="C5" t="n">
-        <v>71.24373169913298</v>
+        <v>68.98900674992166</v>
       </c>
       <c r="D5" t="n">
-        <v>77.44255299840093</v>
+        <v>74.41497154673931</v>
       </c>
       <c r="E5" t="n">
-        <v>83.64137429766888</v>
+        <v>79.84093634355696</v>
       </c>
       <c r="F5" t="n">
-        <v>89.84019559693681</v>
+        <v>85.26690114037461</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.62997946991497</v>
+        <v>64.64226310627329</v>
       </c>
       <c r="C6" t="n">
-        <v>72.82880076918291</v>
+        <v>70.06822790309094</v>
       </c>
       <c r="D6" t="n">
-        <v>79.02762206845085</v>
+        <v>75.4941926999086</v>
       </c>
       <c r="E6" t="n">
-        <v>85.22644336771882</v>
+        <v>80.92015749672626</v>
       </c>
       <c r="F6" t="n">
-        <v>91.42526466698673</v>
+        <v>86.3461222935439</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>76.62</v>
+        <v>73.84999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>76.76000000000001</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>76.81</v>
+        <v>73.98</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.33575039357001</v>
+        <v>73.16179261912482</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76.42261809795509</v>
+        <v>76.21961466426849</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66.13305908333815</v>
+        <v>66.02687451378961</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.715697285094236</v>
+        <v>1.714625711553503</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>71456.09659505378</v>
+        <v>72587.49115548242</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3814208420171</v>
+        <v>1.405599080268037</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1576.69607308248</v>
+        <v>1566.529386662812</v>
       </c>
     </row>
     <row r="3">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3827.34803772526</v>
+        <v>3817.181351305592</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76.42261809795509</v>
+        <v>76.21961466426849</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>76.42261809795509</v>
+        <v>76.21961466426849</v>
       </c>
     </row>
     <row r="15">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>79.58068985311942</v>
+        <v>79.44640157255962</v>
       </c>
       <c r="F11" t="n">
-        <v>62.92612625021227</v>
+        <v>62.81994168066372</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>66.13305908333815</v>
+        <v>66.02687451378961</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60.32537849359611</v>
+        <v>60.18621227403996</v>
       </c>
       <c r="C2" t="n">
-        <v>65.75134329041376</v>
+        <v>65.59478129341309</v>
       </c>
       <c r="D2" t="n">
-        <v>71.17730808723141</v>
+        <v>71.00335031278622</v>
       </c>
       <c r="E2" t="n">
-        <v>76.60327288404908</v>
+        <v>76.41191933215936</v>
       </c>
       <c r="F2" t="n">
-        <v>82.02923768086673</v>
+        <v>81.8204883515325</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.4045996467654</v>
+        <v>61.26543342720925</v>
       </c>
       <c r="C3" t="n">
-        <v>66.83056444358306</v>
+        <v>66.67400244658238</v>
       </c>
       <c r="D3" t="n">
-        <v>72.25652924040071</v>
+        <v>72.08257146595552</v>
       </c>
       <c r="E3" t="n">
-        <v>77.68249403721838</v>
+        <v>77.49114048532866</v>
       </c>
       <c r="F3" t="n">
-        <v>83.10845883403601</v>
+        <v>82.89970950470179</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62.4838207999347</v>
+        <v>62.34465458037855</v>
       </c>
       <c r="C4" t="n">
-        <v>67.90978559675236</v>
+        <v>67.75322359975168</v>
       </c>
       <c r="D4" t="n">
-        <v>73.33575039357001</v>
+        <v>73.16179261912482</v>
       </c>
       <c r="E4" t="n">
-        <v>78.76171519038766</v>
+        <v>78.57036163849796</v>
       </c>
       <c r="F4" t="n">
-        <v>84.18767998720531</v>
+        <v>83.97893065787109</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.56304195310399</v>
+        <v>63.42387573354785</v>
       </c>
       <c r="C5" t="n">
-        <v>68.98900674992166</v>
+        <v>68.83244475292096</v>
       </c>
       <c r="D5" t="n">
-        <v>74.41497154673931</v>
+        <v>74.24101377229411</v>
       </c>
       <c r="E5" t="n">
-        <v>79.84093634355696</v>
+        <v>79.64958279166724</v>
       </c>
       <c r="F5" t="n">
-        <v>85.26690114037461</v>
+        <v>85.05815181104037</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.64226310627329</v>
+        <v>64.50309688671715</v>
       </c>
       <c r="C6" t="n">
-        <v>70.06822790309094</v>
+        <v>69.91166590609026</v>
       </c>
       <c r="D6" t="n">
-        <v>75.4941926999086</v>
+        <v>75.32023492546341</v>
       </c>
       <c r="E6" t="n">
-        <v>80.92015749672626</v>
+        <v>80.72880394483654</v>
       </c>
       <c r="F6" t="n">
-        <v>86.3461222935439</v>
+        <v>86.13737296420967</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>73.84999999999999</v>
+        <v>73.68000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>73.95</v>
+        <v>73.77</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>73.98</v>
+        <v>73.81</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.16179261912482</v>
+        <v>72.23166452031508</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66.02687451378961</v>
+        <v>62.92644751775715</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56250</v>
+        <v>51450</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77250</v>
+        <v>55675</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.714625711553503</v>
+        <v>1.804044156408926</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72587.49115548242</v>
+        <v>67989.56130382058</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.405599080268037</v>
+        <v>1.614290870749556</v>
       </c>
     </row>
   </sheetData>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75000</v>
+        <v>59900</v>
       </c>
       <c r="C2" t="n">
-        <v>57773.96</v>
+        <v>48713.96</v>
       </c>
       <c r="D2" t="n">
-        <v>2.536597741136262</v>
+        <v>2.534507345343832</v>
       </c>
       <c r="E2" t="n">
         <v>0.45</v>
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88000</v>
+        <v>59900</v>
       </c>
       <c r="C3" t="n">
-        <v>65573.96000000001</v>
+        <v>48713.96</v>
       </c>
       <c r="D3" t="n">
-        <v>3.542044726672914</v>
+        <v>2.534507345343832</v>
       </c>
       <c r="E3" t="n">
         <v>0.45</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82000</v>
+        <v>51450</v>
       </c>
       <c r="C4" t="n">
-        <v>61973.96</v>
+        <v>43643.96</v>
       </c>
       <c r="D4" t="n">
-        <v>3.217027196195702</v>
+        <v>2.304075358728335</v>
       </c>
       <c r="E4" t="n">
         <v>0.45</v>
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64000</v>
+        <v>51450</v>
       </c>
       <c r="C5" t="n">
-        <v>51173.96</v>
+        <v>43643.96</v>
       </c>
       <c r="D5" t="n">
-        <v>1.99550360244368</v>
+        <v>2.304075358728335</v>
       </c>
       <c r="E5" t="n">
         <v>0.45</v>
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59000</v>
+        <v>38000</v>
       </c>
       <c r="C6" t="n">
-        <v>48173.96</v>
+        <v>35573.96</v>
       </c>
       <c r="D6" t="n">
-        <v>1.779426994228311</v>
+        <v>1.623693668328883</v>
       </c>
       <c r="E6" t="n">
         <v>0.45</v>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70000</v>
+        <v>38000</v>
       </c>
       <c r="C7" t="n">
-        <v>54773.96</v>
+        <v>35573.96</v>
       </c>
       <c r="D7" t="n">
-        <v>2.484835134467815</v>
+        <v>1.623693668328883</v>
       </c>
       <c r="E7" t="n">
         <v>0.45</v>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74000</v>
+        <v>38000</v>
       </c>
       <c r="C8" t="n">
-        <v>57173.96</v>
+        <v>35573.96</v>
       </c>
       <c r="D8" t="n">
-        <v>2.838441822741726</v>
+        <v>1.623693668328883</v>
       </c>
       <c r="E8" t="n">
         <v>0.45</v>
@@ -981,13 +981,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56000</v>
+        <v>38000</v>
       </c>
       <c r="C9" t="n">
-        <v>46373.96</v>
+        <v>35573.96</v>
       </c>
       <c r="D9" t="n">
-        <v>1.699075229763166</v>
+        <v>1.623693668328883</v>
       </c>
       <c r="E9" t="n">
         <v>0.45</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>79.44640157255962</v>
+        <v>75.52538920636991</v>
       </c>
       <c r="F11" t="n">
-        <v>62.81994168066372</v>
+        <v>59.71951468463127</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>66.02687451378961</v>
+        <v>62.92644751775715</v>
       </c>
     </row>
     <row r="13">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77250</v>
+        <v>55675</v>
       </c>
     </row>
   </sheetData>
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60.18621227403996</v>
+        <v>59.53512260487314</v>
       </c>
       <c r="C2" t="n">
-        <v>65.59478129341309</v>
+        <v>64.94369162424627</v>
       </c>
       <c r="D2" t="n">
-        <v>71.00335031278622</v>
+        <v>70.35226064361942</v>
       </c>
       <c r="E2" t="n">
-        <v>76.41191933215936</v>
+        <v>75.76082966299255</v>
       </c>
       <c r="F2" t="n">
-        <v>81.8204883515325</v>
+        <v>81.16939868236568</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.26543342720925</v>
+        <v>60.47482454322098</v>
       </c>
       <c r="C3" t="n">
-        <v>66.67400244658238</v>
+        <v>65.88339356259411</v>
       </c>
       <c r="D3" t="n">
-        <v>72.08257146595552</v>
+        <v>71.29196258196724</v>
       </c>
       <c r="E3" t="n">
-        <v>77.49114048532866</v>
+        <v>76.70053160134039</v>
       </c>
       <c r="F3" t="n">
-        <v>82.89970950470179</v>
+        <v>82.10910062071352</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62.34465458037855</v>
+        <v>61.41452648156881</v>
       </c>
       <c r="C4" t="n">
-        <v>67.75322359975168</v>
+        <v>66.82309550094195</v>
       </c>
       <c r="D4" t="n">
-        <v>73.16179261912482</v>
+        <v>72.23166452031508</v>
       </c>
       <c r="E4" t="n">
-        <v>78.57036163849796</v>
+        <v>77.64023353968823</v>
       </c>
       <c r="F4" t="n">
-        <v>83.97893065787109</v>
+        <v>83.04880255906136</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.42387573354785</v>
+        <v>62.35422841991664</v>
       </c>
       <c r="C5" t="n">
-        <v>68.83244475292096</v>
+        <v>67.76279743928977</v>
       </c>
       <c r="D5" t="n">
-        <v>74.24101377229411</v>
+        <v>73.17136645866292</v>
       </c>
       <c r="E5" t="n">
-        <v>79.64958279166724</v>
+        <v>78.57993547803605</v>
       </c>
       <c r="F5" t="n">
-        <v>85.05815181104037</v>
+        <v>83.9885044974092</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.50309688671715</v>
+        <v>63.29393035826448</v>
       </c>
       <c r="C6" t="n">
-        <v>69.91166590609026</v>
+        <v>68.70249937763761</v>
       </c>
       <c r="D6" t="n">
-        <v>75.32023492546341</v>
+        <v>74.11106839701074</v>
       </c>
       <c r="E6" t="n">
-        <v>80.72880394483654</v>
+        <v>79.51963741638389</v>
       </c>
       <c r="F6" t="n">
-        <v>86.13737296420967</v>
+        <v>84.92820643575702</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>73.68000000000001</v>
+        <v>72.66</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>73.77</v>
+        <v>72.73999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>73.81</v>
+        <v>72.76000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.08</v>
+        <v>76.15000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67989.56130382058</v>
+        <v>68460.16964949702</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.614290870749556</v>
+        <v>1.625464626566706</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68460.16964949702</v>
+        <v>68460.16964949701</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68460.16964949701</v>
+        <v>68460.16964949702</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.15000000000001</v>
+        <v>79.41</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68460.16964949701</v>
+        <v>90377.07260528322</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.625464626566706</v>
+        <v>2.145842397479628</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79.41</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90377.07260528322</v>
+        <v>75519.2948346429</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.145842397479628</v>
+        <v>1.793070963823935</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77.2</v>
+        <v>78.03</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75519.2948346429</v>
+        <v>81099.3652190915</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.793070963823935</v>
+        <v>1.925559782798697</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>81099.3652190915</v>
+        <v>81099.36521909149</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/stng_fv_report.xlsx
+++ b/outputs/stng_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>81099.36521909149</v>
+        <v>81099.3652190915</v>
       </c>
     </row>
     <row r="16">
